--- a/导出数据2.xlsx
+++ b/导出数据2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\军哥\Desktop\新建文件夹 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\open_workspace\cdzjbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF7B72-C929-438E-8362-F25863C7B3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C6F51A-082B-44F3-988C-D184C4091D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="客户档案" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -114,13 +114,25 @@
   </si>
   <si>
     <t>0.25/下40</t>
+  </si>
+  <si>
+    <t>分类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金,现金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒水,黄金,手机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -138,6 +150,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,11 +196,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -672,124 +694,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.625" customWidth="1"/>
-    <col min="2" max="2" width="27.625" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="14.375" customWidth="1"/>
-    <col min="5" max="5" width="39.625" customWidth="1"/>
-    <col min="6" max="6" width="31.25" customWidth="1"/>
-    <col min="7" max="7" width="28.75" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="184.75" customWidth="1"/>
-    <col min="10" max="10" width="96" customWidth="1"/>
-    <col min="11" max="11" width="40.75" customWidth="1"/>
-    <col min="12" max="12" width="44.375" customWidth="1"/>
+    <col min="1" max="1" width="33.61328125" customWidth="1"/>
+    <col min="2" max="3" width="27.61328125" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="14.3828125" customWidth="1"/>
+    <col min="6" max="6" width="39.61328125" customWidth="1"/>
+    <col min="7" max="7" width="31.23046875" customWidth="1"/>
+    <col min="8" max="8" width="28.765625" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="184.765625" customWidth="1"/>
+    <col min="11" max="11" width="96" customWidth="1"/>
+    <col min="12" max="12" width="40.765625" customWidth="1"/>
+    <col min="13" max="13" width="44.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
